--- a/docs/workbook-split/dateien/Import Stunden.xlsx
+++ b/docs/workbook-split/dateien/Import Stunden.xlsx
@@ -1548,6 +1548,8 @@
       <c r="N60" s="1" t="n"/>
       <c r="O60" s="1" t="n"/>
     </row>
+    <row r="61"/>
+    <row r="62"/>
     <row r="63">
       <c r="C63" t="inlineStr">
         <is>
